--- a/template_bukti_dukung/INDIKATOR_12_TANGGAP_INSIDEN_CSIRT/Template_Log_Register_Insiden_Keamanan_Siber_CSIRT_Indikator12.xlsx
+++ b/template_bukti_dukung/INDIKATOR_12_TANGGAP_INSIDEN_CSIRT/Template_Log_Register_Insiden_Keamanan_Siber_CSIRT_Indikator12.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriks Bukti Dukung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_KPI_CSIRT" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log_Register_Insiden" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analisis_Triase_dan_Forensik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Direktori_Kontak_Eskalasi" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,27 +31,85 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E3A8A"/>
+      <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="00595959"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00274E13"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="004C1130"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000C343D"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B5394"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E4620"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +118,68 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C3D9FF"/>
+        <bgColor rgb="00C3D9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD1DC"/>
+        <bgColor rgb="00EAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E0E3"/>
+        <bgColor rgb="00D0E0E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+        <bgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,38 +193,87 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D3D3D3"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,222 +640,1128 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="82" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="81" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LOG REGISTER PENANGANAN INSIDEN SIBER &amp; REKAPITULASI TRIKAP CSIRT</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>DASHBOARD PEMANTAUAN &amp; METRIK KINERJA CSIRT TAHUN 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pencatatan Insiden Keamanan Informasi Sesuai Standar Panduan Penanganan Insiden BSSN</t>
+          <t>Indikator 12 Evaluasi Pemerintahan Digital (Standar Level 4 &amp; 5 - Terpadu BSSN)</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Total Tiket Insiden 2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Tuntas Tertangani (Resolved)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sedang Investigasi (Open)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata Waktu Tanggap (MTTD)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Rata-rata Pemulihan (MTTR)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Laporan Terkirim ke Gov-CSIRT BSSN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>14 Menit</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>2 Jam 15 Mnt</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>REKAPITULASI INSIDEN BERDASARKAN VEKTOR SERANGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>ID Insiden</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Vektor / Jenis Insiden Siber</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Jumlah Kejadian</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Tingkat Keparahan Dominan</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Status Mitigasi</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Rekomendasi Utama</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Web Defacement (Perubahan Tampilan / Sisipan Judi Online)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi (Sev-2)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Perketat sanitasi upload file, WAF, dan scanning web shell otomatis harian</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Percobaan Brute Force Login &amp; Unauthorized Access</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Sedang (Sev-3)</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Implementasi Multi-Factor Authentication (MFA) &amp; IP Rate Limiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Phishing Email Mengatasnamakan Pejabat/Naskah Dinas</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Sedang (Sev-3)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Security Awareness Training ASN &amp; konfigurasi DMARC/DKIM/SPF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Serangan Distributed Denial of Service (DDoS)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Tinggi (Sev-2)</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Integrasi proteksi CDN scrubbing center PDN &amp; routing BGP filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Penyusupan Ransomware / Enkripsi Data</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Kritis (Sev-1)</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>100% Selesai</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Pemisahan jaringan backup (Air-gapped) &amp; implementasi EDR pada endpoint server</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="67" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BUKU REGISTER PENANGANAN TIKET INSIDEN SIBER INSTANSI TAHUN 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>No. Tiket CSIRT</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Waktu Deteksi</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Sistem Terdampak</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Jenis Serangan</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Tingkat Keparahan</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Waktu Respon Awal</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Waktu Pemulihan (RTO)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Status Penanganan</t>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>Pelapor / Sumber Deteksi</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>Sistem / Aplikasi Terdampak</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Vektor Serangan</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>Keparahan</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>Lead Incident Handler</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>Waktu Respon (MTTD)</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>Waktu Pemulihan (MTTR)</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="inlineStr">
+        <is>
+          <t>No. Laporan BSSN</t>
+        </is>
+      </c>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Status Tiket</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-001</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2026-01-12 03:22</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Alert SIEM Wazuh</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Portal Berita Daerah (dinas.daerah.go.id)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Web Defacement (Judi Online)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi (Sev-2)</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Rizky Pratama, S.Kom</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>8 Menit</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>1 Jam 10 Mnt</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0291</t>
+        </is>
+      </c>
+      <c r="K4" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>INC-2026-001</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>12/01/2026 02:15</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Subdomain Portal Pariwisata</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Web Defacement (Judi Online)</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Tinggi</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>8 Menit</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-002</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-25 14:10</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Helpdesk OPD Bappeda</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Email Resmi Subbag Umum</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Phishing Naskah Palsu</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Sedang (Sev-3)</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Dewi Kartika, S.ST</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>15 Menit</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>45 Menit</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Closed (Remediated)</t>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0344</t>
+        </is>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>INC-2026-002</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>18/02/2026 10:30</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Mail Server Zimbra OPD</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Brute-force Authentication Attack</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Sedang</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-003</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2026-02-04 22:45</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Sensor IDS Suricata</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Aplikasi SIMPEG Kepegawaian</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>SQL Injection Massal</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi (Sev-2)</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Ahmad Fauzi, S.Kom</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>12 Menit</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>2 Jam 05 Mnt</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0412</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-02-004</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-18 08:30</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Laporan Operator SIMDA</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Server File Keuangan BPKAD</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Trojan Backdoor Terdeteksi</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Sedang (Sev-3)</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>Rizky Pratama, S.Kom</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>10 Menit</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>1 Jam 30 Mnt</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0518</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-03-005</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:15</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Monitoring Bandwidth NOC</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Gateway Jaringan Kantor Utama</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>SYN Flood DDoS Attack</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi (Sev-2)</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Budi Santoso, S.T.</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>6 Menit</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>55 Menit</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0620</t>
+        </is>
+      </c>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-03-006</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-14 19:20</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Alert Endpoint EDR</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Server Database Simpus Dinkes</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Percobaan Eksekusi Ransomware</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>Kritis (Sev-1)</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Tim Forensik Gabungan</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>5 Menit</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>15 Menit (IP Banned)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Closed (Remediated)</t>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>3 Jam 40 Mnt</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>BSSN-NOTIF-0701</t>
+        </is>
+      </c>
+      <c r="K9" s="19" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="77" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="67" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="84" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>LEMBAR KERJA ANALISIS TRIASE &amp; ARTEFAK FORENSIK DIGITAL (CHAIN OF CUSTODY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>No Tiket</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>Nama Artefak / Log File</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Tipe Bukti</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="inlineStr">
+        <is>
+          <t>IP Address Penyerang / C2</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Nilai Hash SHA-256 (Integritas)</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Temuan Teknis &amp; Celah Terekploitasi</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Tindakan Netralisasi / Hardening</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Penyidik Forensik</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-001</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>access_log_nginx_20260112.tar.gz</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Server Access Log</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>185.220.101.42 (Tor Exit Node)</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>e3b0c44298fc1c149afbf4c8996fb92427ae41e4649b934ca495991b7852b855</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Injeksi PHP shell via celah plugin form upload yang belum diupdate</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>Isolasi web directory, patch plugin versi terbaru, WAF rule blocking pattern</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>Ahmad Fauzi, S.Kom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-003</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>mysql_query_audit_20260204.log</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Database Query Log</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>103.145.22.18 (Proxy Luar)</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>a1b2c3d4e5f67890123456789abcdef0123456789abcdef0123456789abcdef0</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Union-based SQL Injection pada parameter id_pegawai modul mutasi</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Refactor parameterized query PDO, validasi tipe data input, blacklist keyword</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>Rizky Pratama, S.Kom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>INC-CSIRT-2026-006</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>memory_dump_srvdb01.raw</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>RAM Forensics Volatility</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>194.26.29.112 (Command &amp; Control)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>b8f042e88a09bc11394f42013824ab1190bcdae34120934ca4819234b7851234</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Injeksi proses rundll32.exe mencurigakan mencoba mengenkripsi direktori /data</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>Kill PID terinfeksi, restore snapshot VM sebelum infeksi, blokir port egress 4444</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>Dewi Kartika, S.ST</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="69" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="37" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>MATRIKS DIREKTORI KONTAK DARURAT TIM CSIRT &amp; GOV-CSIRT BSSN (24/7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Entitas / Lembaga</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Peran dalam Eskalasi</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Nama Pejabat / Posko</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Nomor Telepon Darurat</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Email Resmi</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Saluran Terenkripsi (PGP / Signal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Tim CSIRT Instansi Internal</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Incident Commander</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Ketua CSIRT Daerah</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>0812-9999-CSIRT</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>csirt@daerah.go.id</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>PGP Key: 0x9B4D2F1A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Pengelola Data Center Kominfo</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Infrastruktur &amp; Jaringan</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Kabid Penyelenggaraan E-Gov</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>0811-2345-6789</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>datacenter@daerah.go.id</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Hotline NOC Internal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Gov-CSIRT Nasional (BSSN)</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Pusat Operasi Keamanan Siber Nasional</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Direktorat Operasi Keamanan Siber BSSN</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>(021) 78833610 / 0811-888-2776</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>bantuan.insiden@bssn.go.id</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Portal: csirt.bssn.go.id</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>INC-2026-003</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>03/03/2026 14:00</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Aplikasi E-Surat Instansi</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Phishing Link Credential Harvest</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Tinggi</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>12 Menit</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>30 Menit (Domain Blocked)</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Closed (Remediated)</t>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Penyedia Cloud PDN (Komdigi)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Penyedia Hosting PDN Nasional</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Helpdesk Cloud PDN Komdigi</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>(021) 3844445</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>layanan.pdn@komdigi.go.id</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>SLA Dukungan PDN 24/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Siber POLRI</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Penegakan Hukum Kejahatan Siber</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Bareskrim Cyber Crime</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>(021) 5234057</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>cybercrime@polri.go.id</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Pelaporan Resmi BAP</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>